--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -1,110 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity_projects\MazeGame\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484714CF-F60B-44D2-A41E-A9AFCD2C2EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="2445" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3510" yWindow="2445" windowWidth="21600" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
-  <si>
-    <t>itemId</t>
-  </si>
-  <si>
-    <t>item_gold</t>
-  </si>
-  <si>
-    <t>金币</t>
-  </si>
-  <si>
-    <t>生命药水</t>
-  </si>
-  <si>
-    <t>item_sword_wood</t>
-  </si>
-  <si>
-    <t>木剑</t>
-  </si>
-  <si>
-    <t>铁剑</t>
-  </si>
-  <si>
-    <t>皮甲</t>
-  </si>
-  <si>
-    <t>item_potion_red</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_sword_iron</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_armor_leather</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>name</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>price</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>items</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>END</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -138,24 +75,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -443,142 +439,666 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col width="20.5" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="14.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="17" bestFit="1" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A2" s="1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>items</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>itemId</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>item_gold</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>金币</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ingredient_carrot</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>胡萝卜</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ingredient_mushroom</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>迷雾蘑菇</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ingredient_lotus_root</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>莲藕</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ingredient_meat</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>精瘦肉</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ingredient_fish</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>河鲜鱼肉</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ingredient_egg</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>鸟蛋</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ingredient_rice</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>稻米</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ingredient_wheat</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>面粉</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ingredient_salt</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>盐</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ingredient_honey</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>蜂蜜</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ingredient_spice</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>迷宫香料</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ingredient_milk</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>牛奶</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>food_carrot_soup</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>胡萝卜暖汤</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>food_mushroom_skewer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>迷雾蘑菇串</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>food_lotus_crisp</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>莲藕脆片</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>food_spiced_egg</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>香料煎蛋</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>food_wheat_cake</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>麦香烤饼</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>food_fish_rice</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>河鲜饭团</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>food_honey_milk</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>蜂蜜热奶</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>food_meat_stew</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>秘境炖肉</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>food_maze_bento</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>探险便当</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>food_feast_platter</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>迷宫丰收拼盘</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>blueprint_maze_energy_small</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>轻装探索图纸</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>blueprint_maze_energy</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>节能步伐图纸</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>blueprint_maze_energy_large</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>迷宫指南针图纸</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>blueprint_craft_double_small</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>灵感火花图纸</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>blueprint_craft_double</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>料理直觉图纸</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>blueprint_craft_double_large</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>大师备餐术图纸</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>blueprint_shop_speed_small</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>热情招呼图纸</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>blueprint_shop_speed</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>醒目招牌图纸</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>blueprint_shop_speed_large</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>黄金营业时段图纸</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>buff_maze_energy_small</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>轻装探索</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>300</v>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>buff_maze_energy</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>节能步伐</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>buff_maze_energy_large</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>迷宫指南针</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>buff_craft_double_small</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>灵感火花</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>buff_craft_double</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>料理直觉</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>buff_craft_double_large</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>大师备餐术</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>buff_shop_speed_small</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>热情招呼</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>buff_shop_speed</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>醒目招牌</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>buff_shop_speed_large</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>黄金营业时段</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{159BD86A-28B5-40A5-9CD6-C1CDE04F739E}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>300</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>